--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>37.38</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.85</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>6.68</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.88</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.57</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.91</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.05</v>
+        <v>-19.36</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-25.15</v>
+        <v>-24.63</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.61</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.49</v>
+        <v>-28.19</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -655,12 +655,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -669,18 +669,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>131.6</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>103.1</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,38 +709,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85.3</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,78 +749,78 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76.5</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74.90000000000001</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74.7</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74.2</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71.8</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>67.7</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mineral Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.5</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="15">
@@ -929,58 +929,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63.8</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.6</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="19">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,27 +1029,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57.4</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54.4</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="22">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54.1</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="23">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="24">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53.1</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
         <v>106.2</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>103.7</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,36 +1259,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>77.90000000000001</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>77.7</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>75.7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,166 +1337,166 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>67.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>66.90000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>59.2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>57.8</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="25">
@@ -1506,23 +1506,23 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-74.8</v>
+        <v>-75.7</v>
       </c>
     </row>
     <row r="4">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.5</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="5">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-59.6</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="15">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.9</v>
+        <v>-55.4</v>
       </c>
     </row>
     <row r="22">
@@ -1906,12 +1906,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1921,31 +1921,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-50.3</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LOV</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lovisa</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.5</v>
+        <v>-49.1</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.36</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.88</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.13</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.88</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.47</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.4</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.08</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.89</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.84</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>37.1</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.14</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.52</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.79</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.44</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.94</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.36</v>
+        <v>-19.65</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-24.63</v>
+        <v>-23.94</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-26</v>
+        <v>-25.44</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.19</v>
+        <v>-27.46</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -669,38 +669,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>147.4</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,27 +709,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>94.09999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93.3</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84.5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78.8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10">
@@ -829,27 +829,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67.90000000000001</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="12">
@@ -869,98 +869,98 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66.2</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64.09999999999999</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59.8</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,58 +969,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.1</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57.9</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,67 +1049,67 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.2</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.9</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>87.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
         <v>77.3</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
         <v>72.40000000000001</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>69.7</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>64.09999999999999</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
         <v>64</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
         <v>61.1</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
         <v>61</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
         <v>59.3</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
         <v>57.7</v>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="26">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
         <v>57.1</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.7</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="4">
@@ -1741,31 +1741,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-60.3</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-60</v>
+        <v>-60.3</v>
       </c>
     </row>
     <row r="15">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-52.6</v>
       </c>
     </row>
     <row r="25">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.69</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.14</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.98</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.39</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.38</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.65</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.35</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="10">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>34.03</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19.41</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.25</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.14</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.63</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.42</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.65</v>
+        <v>-19.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.94</v>
+        <v>-24.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.44</v>
+        <v>-24.38</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.46</v>
+        <v>-27.99</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>142.6</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110.1</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>99</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>91.40000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79.59999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,18 +769,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -789,23 +789,23 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -815,141 +815,141 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68.40000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.7</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="17">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.5</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,78 +1049,78 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53.2</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.3</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.90000000000001</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1398,27 +1398,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1437,27 +1437,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="23">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74</v>
+        <v>-73.8</v>
       </c>
     </row>
     <row r="5">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.5</v>
+        <v>-70.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69.7</v>
+        <v>-69.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1726,31 +1726,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-61.3</v>
+        <v>-61.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-61</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="14">
@@ -1891,31 +1891,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regis Healthcare</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-52.7</v>
+        <v>-53.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Regis Healthcare</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-52.6</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="25">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.67</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.13</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.99</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.41</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.34</v>
+        <v>32.31</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.67</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.11</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.87</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>34.41</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>18.14</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>5.08</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.66</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.58</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.86</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.88</v>
+        <v>-18.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-24.32</v>
+        <v>-23.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.38</v>
+        <v>-24.78</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.99</v>
+        <v>-28.13</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>148</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>102.9</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>97.7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>96.5</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91.2</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="7">
@@ -769,38 +769,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72.3</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,27 +809,27 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71.5</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70.3</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,107 +849,107 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62.6</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.3</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="17">
@@ -969,27 +969,27 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56.4</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56.4</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="19">
@@ -1009,27 +1009,27 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="21">
@@ -1049,87 +1049,87 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53.7</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>51.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>48.4</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.5</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.6</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>87.5</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1327,13 +1327,13 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1346,14 +1346,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.40000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="19">
@@ -1489,7 +1489,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1502,7 +1502,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1515,14 +1515,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69.59999999999999</v>
+        <v>-69.2</v>
       </c>
     </row>
     <row r="8">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.4</v>
+        <v>-55.2</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.76</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.89</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.14</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.09</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.43</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.69</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.35</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.16</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.91</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.85</v>
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>33.77</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>18.09</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>6.37</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.96</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.92</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.32</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.83</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.12</v>
+        <v>-19.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.61</v>
+        <v>-23.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.78</v>
+        <v>-24.67</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.13</v>
+        <v>-28.77</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>133.1</v>
+        <v>158.4</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>102.1</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88.40000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.3</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,47 +769,47 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.09999999999999</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72.90000000000001</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -849,178 +849,178 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67.40000000000001</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59.6</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57.6</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Resolute Mining</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57.4</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.6</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="21">
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52.8</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Evolution Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="24">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>48.4</v>
+        <v>50.8</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.4</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="3">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="6">
@@ -1268,27 +1268,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="23">
@@ -1483,39 +1483,39 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.40000000000001</v>
+        <v>-70.2</v>
       </c>
     </row>
     <row r="6">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.2</v>
+        <v>-54.8</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.84</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.96</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.26</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.17</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.48</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.36</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.73</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.38</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.23</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.97</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87</v>
+        <v>13.95</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>36.21</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.07</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>7.45</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.89</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.96</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.93</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.16</v>
+        <v>-18.83</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.77</v>
+        <v>-24.58</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.67</v>
+        <v>-24.79</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.77</v>
+        <v>-29.4</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -655,41 +655,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>158.4</v>
+        <v>171.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.5</v>
+        <v>137.1</v>
       </c>
     </row>
     <row r="4">
@@ -709,27 +709,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96.40000000000001</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94.2</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,218 +769,218 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.2</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.09999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71.3</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.40000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64.8</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61.7</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60.9</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60.8</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resolute Mining</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,78 +989,78 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,18 +1069,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Evolution Mining</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,58 +1089,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Ora Banda Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.8</v>
+        <v>46.4</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
-        <v>107.1</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>103.8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
-        <v>99.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>88.5</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
         <v>77.3</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>72.8</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="14">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
         <v>68</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1402,36 +1402,36 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>64.09999999999999</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>63.7</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>59.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="24">
@@ -1493,36 +1493,36 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
     </row>
   </sheetData>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-62.4</v>
+        <v>-63.4</v>
       </c>
     </row>
     <row r="12">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-60.3</v>
+        <v>-59.5</v>
       </c>
     </row>
     <row r="15">
@@ -1861,27 +1861,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.8</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1906,46 +1906,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regis Healthcare</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-52.7</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-51</v>
+        <v>-49.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>TNE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>TechnologyOne</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.1</v>
+        <v>-48.8</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.17</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.38</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.49</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.31</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.7</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.53</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.88</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.54</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.35</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.08</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.95</v>
+        <v>13.82</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>30.15</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>6.36</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.67</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.96</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.3</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.83</v>
+        <v>-18.77</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-24.58</v>
+        <v>-22.75</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.79</v>
+        <v>-24.12</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-29.4</v>
+        <v>-28.42</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>171.3</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>137.1</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>83.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -755,12 +755,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,127 +769,127 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.2</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.40000000000001</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77.90000000000001</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -909,47 +909,47 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65.09999999999999</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58.1</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.7</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="17">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,27 +1009,27 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="21">
@@ -1049,38 +1049,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,27 +1089,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ora Banda Mining</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>70.59999999999999</v>
@@ -1346,14 +1346,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
         <v>65</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>57.7</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
         <v>57.1</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.76</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.91</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.14</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.81</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.31</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.32</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.68</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.3</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.18</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>30.39</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="4">
@@ -491,46 +491,46 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>7.26</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>1.78</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.24</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.31</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.77</v>
+        <v>-18.41</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.75</v>
+        <v>-22.04</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.12</v>
+        <v>-25.76</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.42</v>
+        <v>-28.19</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>163.4</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>134.6</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="4">
@@ -709,38 +709,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91.40000000000001</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85.59999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,47 +769,47 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.59999999999999</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.8</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -829,158 +829,158 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.8</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71.40000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.59999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63.4</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59.2</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="22">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="23">
@@ -1089,18 +1089,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -1268,20 +1268,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>77.3</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1294,14 +1294,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>75.90000000000001</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="14">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="23">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -1591,31 +1591,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Tuas</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-75.8</v>
+        <v>-76.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuas</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-73.8</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="5">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.2</v>
+        <v>-70.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1690,33 +1690,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.2</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-63.4</v>
+        <v>-64.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-59.5</v>
+        <v>-58.9</v>
       </c>
     </row>
     <row r="15">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.7</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.88</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.08</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="5">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.27</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.27</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.66</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.26</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.19</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.98</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>31.08</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="4">
@@ -491,46 +491,46 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.96</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.99</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.08</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.41</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.04</v>
+        <v>-22.15</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.76</v>
+        <v>-26.04</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.19</v>
+        <v>-27.36</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>172.9</v>
+        <v>167.1</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>138.6</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="4">
@@ -709,18 +709,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>94.8</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,258 +729,258 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83.7</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79.59999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78.90000000000001</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60.4</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58.5</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58.4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,47 +1029,47 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="23">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.6</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
@@ -1281,20 +1281,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1340,7 +1340,7 @@
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="16">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -1483,13 +1483,13 @@
         <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1502,7 +1502,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1515,7 +1515,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1621,31 +1621,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.09999999999999</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70</v>
+        <v>-69.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.5</v>
+        <v>-63.9</v>
       </c>
     </row>
     <row r="11">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-61.4</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="13">
@@ -1756,27 +1756,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-58.9</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.3</v>
+        <v>-53.9</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.11</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.79</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.24</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.29</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.69</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.33</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.26</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>28.76</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="4">
@@ -491,59 +491,59 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>5.86</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.38</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.39</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.68</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.45</v>
+        <v>-20.27</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.15</v>
+        <v>-22.38</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-26.04</v>
+        <v>-26.64</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.36</v>
+        <v>-28.13</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>167.1</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>127.3</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>96.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -729,138 +729,138 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.7</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="13">
@@ -889,38 +889,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64.8</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,18 +929,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,18 +949,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57.9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,58 +1009,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49.7</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48.9</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1075,57 +1075,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1135,21 +1135,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>45.5</v>
+        <v>44.9</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.5</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="3">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1333,20 +1333,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1418,7 +1418,7 @@
         <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="23">
@@ -1489,7 +1489,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>WGX</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-76.59999999999999</v>
+        <v>-76.7</v>
       </c>
     </row>
     <row r="4">
@@ -1696,31 +1696,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-63.9</v>
+        <v>-64.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-63.4</v>
+        <v>-64.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-62</v>
+        <v>-63.6</v>
       </c>
     </row>
     <row r="13">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-59</v>
+        <v>-59.9</v>
       </c>
     </row>
     <row r="15">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-58.7</v>
+        <v>-58.5</v>
       </c>
     </row>
     <row r="16">
@@ -1876,31 +1876,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.9</v>
+        <v>-53.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.2</v>
+        <v>-53.1</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.68</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.91</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.12</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.83</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.18</v>
+        <v>36.13</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.27</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.71</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.34</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.99</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.88</v>
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>27.47</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>17.07</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="4">
@@ -491,20 +491,20 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>5.98</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.96</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.1</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.11</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.88</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.27</v>
+        <v>-20.32</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.38</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-26.64</v>
+        <v>-26.69</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.13</v>
+        <v>-28.11</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -655,41 +655,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>128.6</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>120.5</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="4">
@@ -729,27 +729,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
@@ -769,87 +769,87 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73.59999999999999</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="12">
@@ -869,47 +869,47 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61.7</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61.5</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="15">
@@ -929,38 +929,38 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,18 +969,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.1</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,18 +989,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,38 +1009,38 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.7</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,107 +1049,107 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Bellevue Gold</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>45.6</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.9</v>
+        <v>42.7</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>105.7</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C3" t="n">
-        <v>103.4</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C4" t="n">
-        <v>99</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C5" t="n">
-        <v>89.09999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" t="n">
-        <v>80.3</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C12" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C13" t="n">
-        <v>70.5</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C17" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C19" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C22" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C23" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C24" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C25" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
     </row>
   </sheetData>
@@ -1636,31 +1636,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.59999999999999</v>
+        <v>-69.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69.2</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="8">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-58.5</v>
+        <v>-58.4</v>
       </c>
     </row>
     <row r="16">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.1</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.66</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.86</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.81</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.13</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.24</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.7</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.32</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.28</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.97</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87</v>
+        <v>13.85</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>25.06</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>17.58</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>3.97</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.41</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.24</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.4</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.9</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.32</v>
+        <v>-16.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.2</v>
+        <v>-19.62</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-26.69</v>
+        <v>-26.38</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.11</v>
+        <v>-27.89</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>125.9</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,38 +689,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>122.2</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91.59999999999999</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,43 +729,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80.59999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -775,21 +775,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.5</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65.8</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,18 +869,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63.6</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="16">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="17">
@@ -969,127 +969,127 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="24">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42.9</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42.7</v>
+        <v>41.1</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>106.1</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>102.2</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
         <v>98.2</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>89.5</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="9">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
         <v>77.3</v>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.8</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1402,36 +1402,36 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
         <v>61.4</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
         <v>60.9</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-76.7</v>
+        <v>-77.7</v>
       </c>
     </row>
     <row r="4">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-75.8</v>
+        <v>-76.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1681,31 +1681,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.59999999999999</v>
+        <v>-65.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.40000000000001</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-63.6</v>
+        <v>-64.3</v>
       </c>
     </row>
     <row r="13">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-58.4</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="16">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-58.2</v>
+        <v>-58.8</v>
       </c>
     </row>
     <row r="17">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.2</v>
+        <v>-53.5</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.55</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.87</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.08</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.8</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.02</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.26</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.72</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.34</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.3</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.94</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.85</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>24.39</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>16.52</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="4">
@@ -491,59 +491,59 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>3.68</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.05</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.19</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.21</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.25</v>
+        <v>-15.72</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-19.62</v>
+        <v>-16.95</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-26.38</v>
+        <v>-24.52</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.89</v>
+        <v>-26.66</v>
       </c>
     </row>
   </sheetData>
@@ -655,61 +655,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>130.7</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126.7</v>
+        <v>124.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120.9</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="5">
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79.09999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.09999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,167 +849,167 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61.4</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60.4</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.7</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.6</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="20">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="21">
@@ -1049,87 +1049,87 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>44.1</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>43.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bellevue Gold</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.1</v>
+        <v>41.8</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>98.2</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="6">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.09999999999999</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1346,14 +1346,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69</v>
+        <v>-68.3</v>
       </c>
     </row>
     <row r="8">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.40000000000001</v>
+        <v>-64.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1771,31 +1771,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-59</v>
+        <v>-59.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-58.8</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="17">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.48</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.83</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.07</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.74</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.96</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.17</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.66</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.29</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.27</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.92</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>23.34</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19.93</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="4">
@@ -491,33 +491,33 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>4.68</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.57</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.35</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.36</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.58</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.72</v>
+        <v>-16.37</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-16.95</v>
+        <v>-18.97</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.52</v>
+        <v>-25.64</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-26.66</v>
+        <v>-27.28</v>
       </c>
     </row>
   </sheetData>
@@ -655,41 +655,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>125.7</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>124.4</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>114.6</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -729,87 +729,87 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>89.8</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.5</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.8</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77.3</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -849,58 +849,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61.9</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61.1</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,67 +949,67 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.3</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="20">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="21">
@@ -1049,47 +1049,47 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>45.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>45.8</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42.3</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.8</v>
+        <v>38.2</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>105.4</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>101.8</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.7</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1353,7 +1353,7 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="18">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="22">
@@ -1496,7 +1496,7 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="25">
@@ -1509,20 +1509,20 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGX</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-77.7</v>
+        <v>-78.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1621,76 +1621,76 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70</v>
+        <v>-70.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.2</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-68.3</v>
+        <v>-69.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.7</v>
+        <v>-68.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-65.7</v>
+        <v>-67.7</v>
       </c>
     </row>
     <row r="10">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.59999999999999</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1756,31 +1756,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-59.9</v>
+        <v>-61.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-59.8</v>
+        <v>-59.9</v>
       </c>
     </row>
     <row r="16">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-59</v>
+        <v>-59.3</v>
       </c>
     </row>
     <row r="17">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.5</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.53</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.16</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.83</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.98</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="8">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.36</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>20.48</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>16.79</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="4">
@@ -491,33 +491,33 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.46</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.94</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.62</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.79</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.37</v>
+        <v>-15.24</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.97</v>
+        <v>-20.38</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.64</v>
+        <v>-25.03</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.28</v>
+        <v>-27.3</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>133.6</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126.9</v>
+        <v>124.6</v>
       </c>
     </row>
     <row r="4">
@@ -709,38 +709,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>92.90000000000001</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>83.5</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,27 +749,27 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81.3</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73.90000000000001</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70.59999999999999</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="11">
@@ -849,118 +849,118 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61.6</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56.1</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56.1</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55.3</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,27 +969,27 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="19">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1029,87 +1029,87 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.4</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="25">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="26">
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>97.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>77.3</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="11">
@@ -1327,26 +1327,26 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.40000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1366,7 +1366,7 @@
         <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1392,7 +1392,7 @@
         <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.09999999999999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="17">
@@ -1411,7 +1411,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1424,14 +1424,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
@@ -1489,27 +1489,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-68.3</v>
+        <v>-68.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1741,31 +1741,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-61.3</v>
+        <v>-61.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-61.2</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="15">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-59.3</v>
+        <v>-59.6</v>
       </c>
     </row>
     <row r="17">
@@ -1816,57 +1816,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.5</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.6</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.4</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1876,46 +1876,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.3</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-52.7</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-50.9</v>
       </c>
     </row>
     <row r="25">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.49</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.96</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.79</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.96</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.23</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.35</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.37</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.84</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -458,27 +458,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.29</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>17.18</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.47</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.92</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.98</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.76</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.24</v>
+        <v>-15.09</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.38</v>
+        <v>-21.75</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.03</v>
+        <v>-25.36</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.3</v>
+        <v>-28.65</v>
       </c>
     </row>
   </sheetData>
@@ -655,141 +655,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>129.2</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>124.6</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>105.7</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>86.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79.5</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77.3</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.8</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -829,198 +829,198 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69.2</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60.1</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50.6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,98 +1029,98 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,18 +1129,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38.8</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1210,7 +1210,7 @@
         <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>98.90000000000001</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="4">
@@ -1262,7 +1262,7 @@
         <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1327,13 +1327,13 @@
         <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1346,14 +1346,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>70.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1405,7 +1405,7 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="18">
@@ -1444,7 +1444,7 @@
         <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="23">
@@ -1496,33 +1496,33 @@
         <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1666,46 +1666,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-68.09999999999999</v>
+        <v>-67.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-67.7</v>
+        <v>-67.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.59999999999999</v>
+        <v>-64.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1720,22 +1720,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65.59999999999999</v>
+        <v>-64.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.3</v>
+        <v>-64.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-61.5</v>
+        <v>-62.4</v>
       </c>
     </row>
     <row r="14">
@@ -1771,31 +1771,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-59.9</v>
+        <v>-60.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-59.6</v>
+        <v>-59.7</v>
       </c>
     </row>
     <row r="17">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52.7</v>
+        <v>-51.7</v>
       </c>
     </row>
     <row r="23">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-50.9</v>
+        <v>-50.8</v>
       </c>
     </row>
     <row r="25">
@@ -1936,12 +1936,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TNE</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TechnologyOne</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.47</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.97</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.78</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.95</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.2</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.78</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.34</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.38</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.86</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.77</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>17.05</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>16.05</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.42</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.01</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.23</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.09</v>
+        <v>-17.08</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.75</v>
+        <v>-20.21</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.36</v>
+        <v>-25.22</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.65</v>
+        <v>-28.59</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>128.2</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,47 +689,47 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106.3</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81.8</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="6">
@@ -755,81 +755,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73.90000000000001</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.7</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>59.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="12">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="15">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.5</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="16">
@@ -949,78 +949,78 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="22">
@@ -1069,27 +1069,27 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39.7</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="5">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" t="n">
         <v>89.7</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C17" t="n">
         <v>64.2</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.9</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" t="n">
         <v>56.5</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="n">
         <v>56</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-62.4</v>
+        <v>-62.7</v>
       </c>
     </row>
     <row r="14">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-60.3</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="16">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.31</v>
+        <v>49.32</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.78</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.1</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.7</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.74</v>
+        <v>35.73</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.07</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.72</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.2</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.34</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>17.49</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>16.25</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.29</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.61</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.11</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-17.08</v>
+        <v>-18.49</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.21</v>
+        <v>-18.62</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-25.22</v>
+        <v>-24.52</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-28.59</v>
+        <v>-27.24</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,67 +669,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>118.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>92.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82.3</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,87 +749,87 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.90000000000001</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79.5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77.3</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.09999999999999</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61.8</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58.1</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57.6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -909,107 +909,107 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50.7</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="20">
@@ -1029,127 +1029,127 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46.2</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.2</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38.8</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.6</v>
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1314,7 +1314,7 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="14">
@@ -1411,27 +1411,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>62.4</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="25">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-78.09999999999999</v>
+        <v>-78.3</v>
       </c>
     </row>
     <row r="4">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-67.40000000000001</v>
+        <v>-66.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-59.7</v>
+        <v>-59.2</v>
       </c>
     </row>
     <row r="17">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-50.8</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="25">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-48.8</v>
+        <v>-48.9</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.32</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.75</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.13</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.69</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.73</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.05</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.76</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.23</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.35</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.78</v>
+        <v>13.82</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.07</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="3">
@@ -478,33 +478,33 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>15.64</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.67</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.67</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.22</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.49</v>
+        <v>-18.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.62</v>
+        <v>-18.58</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-24.52</v>
+        <v>-23.29</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.24</v>
+        <v>-26.57</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>107.9</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,38 +689,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82.8</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76.90000000000001</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,27 +749,27 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76.5</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="8">
@@ -789,47 +789,47 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.09999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="11">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59.8</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,167 +909,167 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50.6</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="23">
@@ -1089,58 +1089,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>39.7</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34.1</v>
+        <v>32.9</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1288,7 @@
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="12">
@@ -1366,7 +1366,7 @@
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>67.7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1405,7 +1405,7 @@
         <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="18">
@@ -1444,7 +1444,7 @@
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="23">
@@ -1509,20 +1509,20 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.40000000000001</v>
+        <v>-67.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.40000000000001</v>
+        <v>-66.3</v>
       </c>
     </row>
     <row r="10">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-64.90000000000001</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.90000000000001</v>
+        <v>-64.8</v>
       </c>
     </row>
     <row r="12">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-62.7</v>
+        <v>-63.7</v>
       </c>
     </row>
     <row r="14">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61</v>
+        <v>-60.9</v>
       </c>
     </row>
     <row r="16">
@@ -1846,27 +1846,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-54.3</v>
+        <v>-56.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.34</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.77</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.14</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.75</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.81</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.04</v>
+        <v>32.01</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.8</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.25</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="10">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.82</v>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.19</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>12.87</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.79</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.38</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.26</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.35</v>
+        <v>-16.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.58</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.29</v>
+        <v>-23.13</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-26.57</v>
+        <v>-25.23</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103.5</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87.7</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="4">
@@ -709,138 +709,138 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78.7</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.8</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73.7</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70.3</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69.40000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,38 +849,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61.9</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55.8</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,267 +889,267 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54.9</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53.1</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52.2</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50.2</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49.2</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.3</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.1</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>L1G</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>L1 Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>37.8</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1288,7 @@
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1353,7 +1353,7 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>69.8</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>66.5</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="17">
@@ -1405,7 +1405,7 @@
         <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>64.3</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="18">
@@ -1418,7 +1418,7 @@
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1470,7 +1470,7 @@
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="23">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="25">
@@ -1509,20 +1509,20 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>NST</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>55.7</v>
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-76.09999999999999</v>
+        <v>-76.3</v>
       </c>
     </row>
     <row r="5">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.09999999999999</v>
+        <v>-70.8</v>
       </c>
     </row>
     <row r="6">
@@ -1681,12 +1681,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1696,61 +1696,61 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.59999999999999</v>
+        <v>-66.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-64.8</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.59999999999999</v>
+        <v>-64.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-63.7</v>
+        <v>-64.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1816,46 +1816,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-56.6</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.4</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.3</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="21">
@@ -1876,76 +1876,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-51.7</v>
+        <v>-52.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>TWE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Treasury Wine Estates</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51</v>
+        <v>-51.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-50.2</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.1</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>Telix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-48.9</v>
+        <v>-49.1</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.42</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.76</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.21</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.83</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.76</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.01</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.83</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.27</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.42</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.8</v>
+        <v>13.81</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>17.72</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>2.99</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.22</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.57</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.460000000000001</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.85</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-17.4</v>
+        <v>-18.29</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.13</v>
+        <v>-23.31</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.23</v>
+        <v>-25.52</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>105.5</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88.8</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73.8</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.2</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -749,78 +749,78 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61.8</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.4</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61.4</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58.7</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,58 +829,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58.2</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57.2</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,267 +889,267 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53.4</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38.2</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37.2</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1G</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 Group</t>
+          <t>Vault Minerals</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.6</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34.4</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33.7</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.7</v>
+        <v>36.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C2" t="n">
         <v>103.4</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C4" t="n">
         <v>96.90000000000001</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C5" t="n">
-        <v>89.8</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>80.09999999999999</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>77.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C9" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>73.7</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C11" t="n">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C13" t="n">
         <v>69.5</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C14" t="n">
-        <v>68.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C15" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C16" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C18" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C20" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="21">
@@ -1454,36 +1454,36 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C21" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C22" t="n">
-        <v>57.8</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C23" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="24">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C24" t="n">
         <v>56.8</v>
@@ -1506,23 +1506,23 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NST</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C26" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-78.3</v>
+        <v>-79.2</v>
       </c>
     </row>
     <row r="4">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-76.3</v>
+        <v>-74.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1630,63 +1630,63 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-70.8</v>
+        <v>-71.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70</v>
+        <v>-69.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69.2</v>
+        <v>-68.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.09999999999999</v>
+        <v>-67.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1696,16 +1696,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-66.3</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="11">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-64.59999999999999</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="14">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.5</v>
+        <v>-57.6</v>
       </c>
     </row>
     <row r="19">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.4</v>
+        <v>-55.3</v>
       </c>
     </row>
     <row r="21">
@@ -1891,46 +1891,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TWE</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Treasury Wine Estates</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51.7</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-50.2</v>
+        <v>-49.5</v>
       </c>
     </row>
     <row r="26">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.35</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.2</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.88</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.79</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.82</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.33</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.47</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.74</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.81</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>19.09</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>14.07</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.45</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.95</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="8">
@@ -543,33 +543,33 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.78</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.86</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.29</v>
+        <v>-18.62</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.31</v>
+        <v>-23.22</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.52</v>
+        <v>-24.8</v>
       </c>
     </row>
   </sheetData>
@@ -655,41 +655,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>108.2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>107.9</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91.3</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -749,18 +749,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69.5</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -769,47 +769,47 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64.40000000000001</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="10">
@@ -829,127 +829,127 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61.9</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -969,47 +969,47 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47.8</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="20">
@@ -1035,21 +1035,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="22">
@@ -1069,58 +1069,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39.6</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38.7</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37.1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>36.7</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36.6</v>
+        <v>33.6</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
         <v>96.90000000000001</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>90.2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>80.5</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
         <v>77.90000000000001</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
         <v>69.5</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
         <v>68.40000000000001</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>55.7</v>
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-79.2</v>
+        <v>-79.5</v>
       </c>
     </row>
     <row r="4">
@@ -1630,52 +1630,52 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-71.59999999999999</v>
+        <v>-72.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.2</v>
+        <v>-69.59999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-68.90000000000001</v>
+        <v>-69.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.7</v>
+        <v>-68.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1801,31 +1801,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-57.7</v>
+        <v>-58.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.6</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="19">
@@ -1876,76 +1876,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-52.6</v>
+        <v>-53.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-51</v>
+        <v>-52.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-50.2</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-49.5</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Telix Pharmaceuticals</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.1</v>
+        <v>-49.4</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.27</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.75</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.17</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.94</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.84</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.96</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.48</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.7</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.83</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>19.02</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>11.58</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5.51</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="6">
@@ -517,33 +517,33 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.98</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.04</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.15</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.5</v>
+        <v>-18.85</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-18.62</v>
+        <v>-19.59</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.22</v>
+        <v>-23.02</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.8</v>
+        <v>-24.91</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95.59999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>93.7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,118 +749,118 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65.3</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63.8</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62.2</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58.3</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56.5</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="14">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,158 +929,158 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49.7</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48.7</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43.4</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.6</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40.7</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vault Minerals</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.7</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34.8</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.6</v>
+        <v>29.7</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>74.2</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="11">
@@ -1324,36 +1324,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>69.5</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="24">
@@ -1493,36 +1493,36 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>LYC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.59999999999999</v>
+        <v>-73.7</v>
       </c>
     </row>
     <row r="5">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-69.59999999999999</v>
+        <v>-70.3</v>
       </c>
     </row>
     <row r="7">
@@ -1696,31 +1696,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-66.2</v>
+        <v>-65.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65.59999999999999</v>
+        <v>-65.5</v>
       </c>
     </row>
     <row r="12">
@@ -1780,18 +1780,18 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-60.9</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1801,16 +1801,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-58.9</v>
+        <v>-59.2</v>
       </c>
     </row>
     <row r="18">
@@ -1936,16 +1936,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.4</v>
+        <v>-49.9</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.23</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.71</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.18</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.93</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.79</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.92</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.78</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.35</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.46</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.69</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.84</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,85 +465,85 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15.72</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>7.86</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>4.74</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-4</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.16</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.85</v>
+        <v>-18.18</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-19.59</v>
+        <v>-21.92</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.02</v>
+        <v>-22.41</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.91</v>
+        <v>-25.03</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88.2</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.40000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="6">
@@ -749,78 +749,78 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67.59999999999999</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.1</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58.8</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,78 +829,78 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56.5</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.1</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,18 +909,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,118 +929,118 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48.1</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44.1</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,107 +1049,107 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32.6</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>FPH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Fisher &amp; Paykel Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.7</v>
+        <v>27.7</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.1</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.09999999999999</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1314,7 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1340,46 +1340,46 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.40000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1405,7 +1405,7 @@
         <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="18">
@@ -1431,7 +1431,7 @@
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1470,7 @@
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="23">
@@ -1509,7 +1509,7 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.2</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.2</v>
+        <v>56.5</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1552,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-79.5</v>
+        <v>-79.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-73.7</v>
+        <v>-74.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-72.90000000000001</v>
+        <v>-72.2</v>
       </c>
     </row>
     <row r="6">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70.3</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="7">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65.5</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1741,61 +1741,61 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-63</v>
+        <v>-63.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-61.3</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61.1</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-59.2</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="17">
@@ -1855,37 +1855,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.3</v>
+        <v>-55.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.3</v>
+        <v>-55.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.9</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="23">
@@ -1906,46 +1906,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catalyst Metals</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-51</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Netwealth Group</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-50.2</v>
+        <v>-52.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49.9</v>
+        <v>-51.3</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.21</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.67</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.22</v>
+        <v>44.41</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.02</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.81</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.8</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.79</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.5</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.72</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.86</v>
+        <v>13.94</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>13.01</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>7.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3.67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="6">
@@ -517,59 +517,59 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>0.23</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.91</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.43</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.18</v>
+        <v>-18.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.92</v>
+        <v>-19.61</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-22.41</v>
+        <v>-22.26</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-25.03</v>
+        <v>-23.68</v>
       </c>
     </row>
   </sheetData>
@@ -669,47 +669,47 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121.7</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85.09999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80.7</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.3</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63.3</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="7">
@@ -769,78 +769,78 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62.7</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53.8</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,87 +849,87 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="16">
@@ -949,27 +949,27 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.9</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40.2</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="18">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38.7</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="19">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38.2</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.8</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.1</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="23">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FPH</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fisher &amp; Paykel Healthcare</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Perseus Mining</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1275,7 +1275,7 @@
         <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1301,26 +1301,26 @@
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="13">
@@ -1353,33 +1353,33 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="17">
@@ -1411,27 +1411,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="25">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.5</v>
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -1621,31 +1621,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-72.2</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-72</v>
+        <v>-71.5</v>
       </c>
     </row>
     <row r="7">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-68.90000000000001</v>
+        <v>-68.7</v>
       </c>
     </row>
     <row r="9">
@@ -1696,27 +1696,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.59999999999999</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.8</v>
+        <v>-64.3</v>
       </c>
     </row>
     <row r="13">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-63.1</v>
+        <v>-63.9</v>
       </c>
     </row>
     <row r="14">
@@ -1846,31 +1846,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.6</v>
+        <v>-55.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.5</v>
+        <v>-55.4</v>
       </c>
     </row>
     <row r="22">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.33</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.91</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.41</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.13</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.86</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.88</v>
+        <v>27.87</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.46</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.57</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.77</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.94</v>
+        <v>13.98</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>12.88</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>6.45</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="4">
@@ -491,33 +491,33 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.87</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.12</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.34</v>
+        <v>-18.25</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-19.61</v>
+        <v>-20.77</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-22.26</v>
+        <v>-21.92</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.68</v>
+        <v>-22.26</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>111.9</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>90.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80.3</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>77.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,118 +749,118 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69.7</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59.4</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>57.8</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53.8</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,18 +889,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,58 +909,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46.3</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="18">
@@ -989,158 +989,158 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39.1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36.9</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32.3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31.1</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.1</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Perseus Mining</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>32.9</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
         <v>103.1</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
         <v>80.7</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>72.90000000000001</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="12">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
         <v>69.8</v>
@@ -1350,36 +1350,36 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1402,36 +1402,36 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="22">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
         <v>57.4</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
         <v>57.2</v>
@@ -1489,40 +1489,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LYC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.3</v>
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-72</v>
+        <v>-73.5</v>
       </c>
     </row>
     <row r="6">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-71.5</v>
+        <v>-70.8</v>
       </c>
     </row>
     <row r="7">
@@ -1726,12 +1726,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1741,16 +1741,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-63.9</v>
+        <v>-64.2</v>
       </c>
     </row>
     <row r="14">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-63</v>
+        <v>-62.4</v>
       </c>
     </row>
     <row r="15">
@@ -1855,37 +1855,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-55.5</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.4</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.3</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="23">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.41</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.93</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.44</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.15</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.95</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.96</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.87</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.51</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.58</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.76</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.18</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>8.07</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5.33</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>3.01</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.64</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.84</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.25</v>
+        <v>-18.09</v>
       </c>
     </row>
     <row r="10">
@@ -569,33 +569,33 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.77</v>
+        <v>-20.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.92</v>
+        <v>-21.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.26</v>
+        <v>-21.85</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>124.3</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.09999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78.40000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71.5</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,87 +769,87 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66.09999999999999</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="12">
@@ -869,27 +869,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -909,38 +909,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49.7</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48.6</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="17">
@@ -969,138 +969,138 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45.9</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41.1</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>39.2</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35.7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>90.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" t="n">
         <v>70.7</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="17">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="19">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="n">
         <v>61.6</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="n">
         <v>57.2</v>
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1606,31 +1606,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liontown Resources</t>
+          <t>Deep Yellow</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.2</v>
+        <v>-74.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deep Yellow</t>
+          <t>Liontown Resources</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-73.5</v>
+        <v>-74.2</v>
       </c>
     </row>
     <row r="6">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.3</v>
+        <v>-64.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.19</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.85</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.24</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.21</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.82</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.85</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.48</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.52</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.9</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.95</v>
+        <v>13.94</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,33 +465,33 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>16.04</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>6.96</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>5.91</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>2.51</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="6">
@@ -517,85 +517,85 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.91</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.03</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.09</v>
+        <v>-20.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.68</v>
+        <v>-21.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.72</v>
+        <v>-21.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>-21.85</v>
+        <v>-21.86</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>116.2</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88.3</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.5</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -789,47 +789,47 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59.3</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="11">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>59.1</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52.4</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="14">
@@ -909,47 +909,47 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48.3</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.9</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.6</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="17">
@@ -969,127 +969,127 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>41.7</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>41.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38.4</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37.7</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="24">
@@ -1109,18 +1109,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>DNL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Dyno Nobel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.8</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FPH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>Fisher &amp; Paykel Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.7</v>
+        <v>28.8</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="7">
@@ -1314,7 +1314,7 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -1353,13 +1353,13 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1372,14 +1372,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="16">
@@ -1418,7 +1418,7 @@
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="19">
@@ -1463,66 +1463,66 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>57.3</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.5</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>VAU</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -1666,16 +1666,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>NextDC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-68.7</v>
+        <v>-67.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1696,27 +1696,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.09999999999999</v>
+        <v>-65.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1726,132 +1726,132 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.59999999999999</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-64.2</v>
+        <v>-64.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-62.4</v>
+        <v>-64.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61.3</v>
+        <v>-62.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-61.1</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-59.2</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-57.7</v>
+        <v>-59.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-56.6</v>
+        <v>-57.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1861,91 +1861,91 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.3</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.4</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-52.6</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-52.5</v>
+        <v>-52.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Netwealth Group</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-52.4</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Netwealth Group</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-51.3</v>
+        <v>-52.4</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.15</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.81</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.25</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.18</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.85</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.84</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.47</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.51</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.93</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.94</v>
+        <v>13.97</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>16.97</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>6.74</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>4.9</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.79</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.13</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.23</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="9">
@@ -556,46 +556,46 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.08</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.32</v>
+        <v>-21.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.34</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>-21.86</v>
+        <v>-22.8</v>
       </c>
     </row>
   </sheetData>
@@ -669,27 +669,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>113.3</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82.7</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="4">
@@ -709,27 +709,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78.59999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70.40000000000001</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="9">
@@ -809,87 +809,87 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60.2</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59.7</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56.2</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.4</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46.3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -909,178 +909,178 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.8</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38.8</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36.2</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.5</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1089,67 +1089,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.8</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DNL</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dyno Nobel</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.3</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FPH</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fisher &amp; Paykel Healthcare</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.8</v>
+        <v>32.6</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>93.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="13">
@@ -1366,7 +1366,7 @@
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1411,27 +1411,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.7</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.6</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="20">
@@ -1444,59 +1444,59 @@
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.3</v>
+        <v>55.6</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-74.7</v>
+        <v>-75.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70.8</v>
+        <v>-70.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1696,27 +1696,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.5</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1726,16 +1726,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-65.09999999999999</v>
+        <v>-64.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-62.4</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="16">
@@ -1846,27 +1846,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.6</v>
+        <v>-57.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-52.4</v>
+        <v>-51.8</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.12</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.08</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.27</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.24</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="6">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.82</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.83</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.52</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.98</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.97</v>
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>14.83</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="3">
@@ -478,46 +478,46 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>7.79</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7.72</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.51</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.45</v>
+        <v>-19.6</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.16</v>
+        <v>-20.69</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.59</v>
+        <v>-20.73</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>-22.8</v>
+        <v>-23.21</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103.8</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80.7</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,138 +709,138 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.8</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64.40000000000001</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61.3</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,138 +849,138 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49.9</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44.2</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>41.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39.6</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -989,167 +989,167 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38.6</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36.7</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.9</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.6</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FPH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>Fisher &amp; Paykel Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.6</v>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="4">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>80.09999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="7">
@@ -1281,27 +1281,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>OBM</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>77.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OBM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.7</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>70.8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>69.7</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1353,33 +1353,33 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="16">
@@ -1418,7 +1418,7 @@
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.2</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="19">
@@ -1431,7 +1431,7 @@
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>60.9</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="20">
@@ -1444,7 +1444,7 @@
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1470,7 +1470,7 @@
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>59.4</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="23">
@@ -1483,7 +1483,7 @@
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>55.6</v>
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-75.40000000000001</v>
+        <v>-76.8</v>
       </c>
     </row>
     <row r="5">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-74.2</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="6">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70.40000000000001</v>
+        <v>-70.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1681,42 +1681,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.3</v>
+        <v>-66.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-65.09999999999999</v>
+        <v>-66.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1726,27 +1726,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.90000000000001</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-64.2</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="15">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-62</v>
+        <v>-61.7</v>
       </c>
     </row>
     <row r="16">
@@ -1816,46 +1816,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-59.2</v>
+        <v>-60.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-57.7</v>
+        <v>-59.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-57.3</v>
+        <v>-57.1</v>
       </c>
     </row>
     <row r="21">
@@ -1891,31 +1891,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.4</v>
+        <v>-53.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-52.6</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="25">
@@ -1930,22 +1930,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-52.5</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Netwealth Group</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-51.8</v>
+        <v>-52.6</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.1</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.26</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.21</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.26</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.98</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.9</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.53</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.56</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>11.18</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="3">
@@ -478,33 +478,33 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>6.64</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>1.64</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.5</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.99</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="9">
@@ -556,33 +556,33 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.6</v>
+        <v>-18.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.69</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-20.73</v>
+        <v>-22.75</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.21</v>
+        <v>-24.11</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,18 +689,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.8</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,178 +749,178 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.3</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59.6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39.3</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38.9</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,127 +929,127 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38.1</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>36.9</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36.7</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="22">
@@ -1069,87 +1069,87 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LSF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>L1 Long Short Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FPH</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fisher &amp; Paykel Healthcare</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.6</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.6</v>
+        <v>32.4</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="3">
@@ -1220,20 +1220,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" t="n">
         <v>95.8</v>
@@ -1242,14 +1242,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C5" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>85.2</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>77.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" t="n">
         <v>73.09999999999999</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C12" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C14" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C16" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C17" t="n">
         <v>65</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>61.6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C19" t="n">
-        <v>61.4</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="22">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C23" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="25">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C25" t="n">
         <v>56.8</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C26" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-79.8</v>
+        <v>-83.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.40000000000001</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="10">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-66.3</v>
+        <v>-66.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1846,31 +1846,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-57.1</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-56.6</v>
+        <v>-55.8</v>
       </c>
     </row>
     <row r="22">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-53.4</v>
+        <v>-53.3</v>
       </c>
     </row>
     <row r="25">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.18</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.39</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.31</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.03</v>
+        <v>36.01</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.86</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.92</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.71</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.59</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.02</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.99</v>
+        <v>13.97</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>5.99</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>3.58</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>0.78</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.45</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.52</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.92</v>
+        <v>-19.33</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.77</v>
+        <v>-22.84</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>-22.75</v>
+        <v>-23.63</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.11</v>
+        <v>-24.08</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>92.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -749,87 +749,87 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>60.7</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56.3</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -849,258 +849,258 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43.4</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>41.3</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41.2</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.2</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37.8</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37.8</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LSF</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 Long Short Fund</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.9</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="25">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Redox</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="6">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="9">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="12">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="13">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="15">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="16">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>66.5</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C17" t="n">
         <v>65</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="20">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="21">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" t="n">
         <v>59.9</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>58.2</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="24">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="25">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="26">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.3</v>
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-83.40000000000001</v>
+        <v>-83.5</v>
       </c>
     </row>
     <row r="4">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-53.3</v>
+        <v>-53.5</v>
       </c>
     </row>
     <row r="25">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-52.6</v>
+        <v>-52.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.1</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.29</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.4</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.28</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.01</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.95</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.72</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.64</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.97</v>
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,59 +465,59 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>13.19</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5.37</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.23</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.47</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.1</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="9">
@@ -556,46 +556,46 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.33</v>
+        <v>-20.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.84</v>
+        <v>-21.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.63</v>
+        <v>-23.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.08</v>
+        <v>-24.9</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -689,58 +689,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>CDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Codan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.40000000000001</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,218 +749,218 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61.5</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDA</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Codan</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60.1</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52.1</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REH</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reece Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>42.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,27 +969,27 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="19">
@@ -1009,98 +1009,98 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38.7</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37.3</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>36.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SFR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Sandfire Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,38 +1109,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34.4</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APA Group</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RDX</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Redox</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>255</v>
       </c>
       <c r="C4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="5">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>85.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>255</v>
       </c>
       <c r="C8" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1301,7 +1301,7 @@
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>76.8</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70.5</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1353,26 +1353,26 @@
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>68.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1385,79 +1385,79 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>66.3</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>255</v>
       </c>
       <c r="C17" t="n">
-        <v>65</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>255</v>
       </c>
       <c r="C19" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>61.2</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>255</v>
       </c>
       <c r="C21" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1483,7 +1483,7 @@
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1696,117 +1696,117 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Life360</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-66.09999999999999</v>
+        <v>-65.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Life360</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65.09999999999999</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-65.09999999999999</v>
+        <v>-64.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-64.8</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-64</v>
+        <v>-61.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61.7</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-61.3</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1855,67 +1855,67 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-56.6</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-55.8</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-54.3</v>
+        <v>-53.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.8</v>
+        <v>-53.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-53.5</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="25">
@@ -1936,16 +1936,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>IGO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-52.7</v>
+        <v>-52.1</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.39</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.45</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.29</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.07</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.92</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.94</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.7</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.62</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="11">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.96</v>
+        <v>14.03</v>
       </c>
     </row>
   </sheetData>

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>13.35</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>11.98</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.62</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.18</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.27</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.35</v>
+        <v>-18.06</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.2</v>
+        <v>-20.87</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.38</v>
+        <v>-23.53</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.9</v>
+        <v>-24.42</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>91.59999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="3">
@@ -689,27 +689,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80.09999999999999</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>Viva Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68.8</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="5">
@@ -729,238 +729,238 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67.2</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Energy</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64.90000000000001</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WOW</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woolworths Group</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55.3</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54.7</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>WOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Woolworths Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48.6</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44.4</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SGM</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sims Metal</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.3</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -969,38 +969,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40.6</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>Electro Optic Systems Holdings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1029,18 +1029,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1049,58 +1049,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>37.8</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SFR</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sandfire Resources</t>
+          <t>Stanmore Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,47 +1109,47 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35.1</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.8</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>31.2</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>96.59999999999999</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="7">
@@ -1275,7 +1275,7 @@
         <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="8">
@@ -1301,7 +1301,7 @@
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1327,7 @@
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>71.5</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1359,27 +1359,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>255</v>
       </c>
       <c r="C15" t="n">
-        <v>68.5</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v>255</v>
       </c>
       <c r="C16" t="n">
-        <v>65.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1463,66 +1463,66 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>255</v>
       </c>
       <c r="C22" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>58.7</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>56.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAU</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-83.5</v>
+        <v>-83.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1636,61 +1636,61 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRO</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Droneshield</t>
+          <t>Champion Iron</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-70.09999999999999</v>
+        <v>-71.59999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COH</t>
+          <t>DRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cochlear</t>
+          <t>Droneshield</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-69.2</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>COH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NextDC</t>
+          <t>Cochlear</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-67.59999999999999</v>
+        <v>-68.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Champion Iron</t>
+          <t>NextDC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-66.7</v>
+        <v>-67.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-64.8</v>
+        <v>-63.9</v>
       </c>
     </row>
     <row r="13">
@@ -1750,48 +1750,48 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-64</v>
+        <v>-63.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-61.6</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61.3</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1801,31 +1801,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-61.1</v>
+        <v>-60.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-60.8</v>
+        <v>-59.8</v>
       </c>
     </row>
     <row r="19">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-59.2</v>
+        <v>-58.3</v>
       </c>
     </row>
     <row r="20">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-58.2</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="21">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.4</v>
+        <v>-53.2</v>
       </c>
     </row>
     <row r="24">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.14</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.42</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.47</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.33</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="6">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.14</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.96</v>
+        <v>31.91</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.02</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.76</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="10">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.04</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="12">

--- a/reports/asx-market-report.xlsx
+++ b/reports/asx-market-report.xlsx
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>12.27</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>9.93</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.35</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="8">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.47</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.06</v>
+        <v>-15.17</v>
       </c>
     </row>
     <row r="10">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.87</v>
+        <v>-20.83</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>-23.53</v>
+        <v>-21.09</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-24.42</v>
+        <v>-22.68</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -655,12 +655,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Ramsay Health Care</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -669,27 +669,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79.2</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ramsay Health Care</t>
+          <t>Alkane Resources</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65.8</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="5">
@@ -729,18 +729,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.09999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>BSL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alkane Resources</t>
+          <t>BlueScope</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,87 +749,87 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62.5</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Hope</t>
+          <t>Predictive Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSL</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BlueScope</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58.3</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>NHC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Predictive Discovery</t>
+          <t>New Hope</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -849,303 +849,303 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>REH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Greatland Resources</t>
+          <t>Reece Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Greatland Resources</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42.7</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NWH</t>
+          <t>S32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NRW Holdings</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>QBE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South32</t>
+          <t>QBE Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>36.5</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CGF</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>NWH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Emerald Resources</t>
+          <t>NRW Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>CGF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Electro Optic Systems Holdings</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QBE</t>
+          <t>ALD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QBE Insurance</t>
+          <t>Ampol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>MND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Monadelphous Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.1</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MND</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monadelphous Group</t>
+          <t>Emerald Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stanmore Resources</t>
+          <t>Dalrymple Bay Infrastructure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33.2</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dalrymple Bay Infrastructure</t>
+          <t>Sims Metal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALD</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ampol</t>
+          <t>APA Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1210,7 +1210,7 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>102.6</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
         <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1301,7 +1301,7 @@
         <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="10">
@@ -1314,59 +1314,59 @@
         <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DYL</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>255</v>
       </c>
       <c r="C11" t="n">
-        <v>71.09999999999999</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>DYL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>255</v>
       </c>
       <c r="C12" t="n">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>255</v>
       </c>
       <c r="C13" t="n">
-        <v>69.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYL</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>68.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1418,7 +1418,7 @@
         <v>255</v>
       </c>
       <c r="C18" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="19">
@@ -1444,7 +1444,7 @@
         <v>255</v>
       </c>
       <c r="C20" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="21">
@@ -1483,7 +1483,7 @@
         <v>255</v>
       </c>
       <c r="C23" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="24">
@@ -1496,7 +1496,7 @@
         <v>255</v>
       </c>
       <c r="C24" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="25">
@@ -1509,7 +1509,7 @@
         <v>255</v>
       </c>
       <c r="C25" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="26">
@@ -1522,7 +1522,7 @@
         <v>255</v>
       </c>
       <c r="C26" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
     </row>
   </sheetData>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-75.8</v>
+        <v>-76.5</v>
       </c>
     </row>
     <row r="6">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-70</v>
+        <v>-71.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-68.5</v>
+        <v>-68.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1711,27 +1711,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GDG</t>
+          <t>4DX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Generation Development Group</t>
+          <t>4DMedical</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-65</v>
+        <v>-64.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>GDG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Generation Development Group</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1741,12 +1741,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XRO</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xero</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1756,42 +1756,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>XRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Austal</t>
+          <t>Xero</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-61.3</v>
+        <v>-62.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PXA</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pexa Group</t>
+          <t>Austal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-61.1</v>
+        <v>-61.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTC</t>
+          <t>PXA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wisetech Global</t>
+          <t>Pexa Group</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1801,151 +1801,151 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>WTC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PLS Group</t>
+          <t>Wisetech Global</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-60.8</v>
+        <v>-61.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pro Medicus</t>
+          <t>PLS Group</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-59.8</v>
+        <v>-60.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Seek</t>
+          <t>Pro Medicus</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-58.3</v>
+        <v>-59.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>CYL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lendlease</t>
+          <t>Catalyst Metals</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-57.2</v>
+        <v>-59.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4DX</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4DMedical</t>
+          <t>Seek</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-54.3</v>
+        <v>-57.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AAI</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alcoa</t>
+          <t>Lendlease</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-53.8</v>
+        <v>-56.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>AAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARB Corporation</t>
+          <t>Alcoa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-53.2</v>
+        <v>-53.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SNZ</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Summerset Group Holdings</t>
+          <t>ARB Corporation</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-53</v>
+        <v>-53.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PDN</t>
+          <t>SNZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paladin Energy</t>
+          <t>Summerset Group Holdings</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-52.7</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>PDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>Paladin Energy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-52.1</v>
+        <v>-52.7</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.04</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="3">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.3</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="4">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.46</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="5">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.32</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="6">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.91</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.08</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="9">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.69</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.68</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="11">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.02</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="12">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.03</v>
+        <v>14.06</v>
       </c>
     </row>
   </sheetData>
